--- a/metrics_summary.xlsx
+++ b/metrics_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vilsonkhchoian/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C597CC18-F8A7-DA4C-90AA-15C0197FE1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D9FDB1-76EE-E146-88C3-27312BFFAE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="36">
   <si>
     <t>model</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Sperman - показывает, насколько хорошо модель сохраняет порядок эссе: сильные эссе должны получать более высокие оценки, слабые — более низкие. Чем ближе к 1, тем лучше ранжирование.</t>
+  </si>
+  <si>
+    <t>prompt_6</t>
   </si>
 </sst>
 </file>
@@ -232,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -252,6 +255,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -554,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -705,7 +714,7 @@
       <c r="F3" s="9">
         <v>4.9085384790179649</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="16">
         <v>63.166889483065937</v>
       </c>
       <c r="H3" s="8">
@@ -739,7 +748,7 @@
         <v>4.2537783864594534</v>
       </c>
       <c r="R3" s="8">
-        <f t="shared" ref="R3:R26" si="0">(0.25*(10-E3)+0.1*(10-F3)+0.15*(10-J3)+0.2*(K3*10)+0.03*(L3*10)+0.08*(M3*10)+0.15*(N3*10)+0.02*(10-Q3)) * 10</f>
+        <f t="shared" ref="R3:R30" si="0">(0.25*(10-E3)+0.1*(10-F3)+0.15*(10-J3)+0.2*(K3*10)+0.03*(L3*10)+0.08*(M3*10)+0.15*(N3*10)+0.02*(10-Q3)) * 10</f>
         <v>30.119720961688401</v>
       </c>
     </row>
@@ -870,105 +879,105 @@
       <c r="D6">
         <v>40</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="13">
         <v>1.1375</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="13">
         <v>1.807968473176454</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="13">
         <v>17.769353195823779</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="13">
         <v>18.839944180346659</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="14">
         <v>-0.33750000000000002</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="14">
         <v>0.33750000000000002</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="14">
         <v>0.82499999999999996</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="14">
         <v>0.9</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="13">
         <v>0.38513399909419171</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="13">
         <v>0.13253012048192761</v>
       </c>
-      <c r="O6" s="3">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="O6" s="13">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P6" s="14">
         <v>7.0250000000000004</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="13">
         <v>3.7809333198005328</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="13">
         <f t="shared" si="0"/>
         <v>70.354868662845888</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7">
-        <v>0.9</v>
-      </c>
-      <c r="F7">
-        <v>1.3462912017836259</v>
-      </c>
-      <c r="G7">
-        <v>11.916825821237589</v>
-      </c>
-      <c r="H7">
-        <v>13.65555416070996</v>
-      </c>
-      <c r="I7">
-        <v>-0.75</v>
-      </c>
-      <c r="J7">
-        <v>0.75</v>
-      </c>
-      <c r="K7">
-        <v>0.8</v>
-      </c>
-      <c r="L7">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="M7">
-        <v>0.54270516725411133</v>
-      </c>
-      <c r="N7">
-        <v>0.53532182103610682</v>
-      </c>
-      <c r="O7">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P7">
-        <v>6.6124999999999998</v>
-      </c>
-      <c r="Q7">
-        <v>8.1885389499890149</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="0"/>
-        <v>76.787469661793068</v>
+      <c r="E7" s="3">
+        <v>2.3875000000000002</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.0852469999999999</v>
+      </c>
+      <c r="G7" s="17">
+        <v>86.335819999999998</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46.92754</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.2124999999999999</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.2124999999999999</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.42009600000000002</v>
+      </c>
+      <c r="N7" s="3">
+        <v>8.7344000000000005E-2</v>
+      </c>
+      <c r="O7" s="3">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P7" s="3">
+        <v>6.875</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>4.1606899999999998</v>
+      </c>
+      <c r="R7" s="3">
+        <f t="shared" si="0"/>
+        <v>55.691043000000001</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -979,53 +988,53 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>40</v>
       </c>
       <c r="E8">
-        <v>4.4375</v>
+        <v>0.9</v>
       </c>
       <c r="F8">
-        <v>4.7110243047558136</v>
+        <v>1.3462912017836259</v>
       </c>
       <c r="G8">
-        <v>59.162109540785998</v>
+        <v>11.916825821237589</v>
       </c>
       <c r="H8">
-        <v>87.474442915484801</v>
+        <v>13.65555416070996</v>
       </c>
       <c r="I8">
-        <v>-4.3375000000000004</v>
+        <v>-0.75</v>
       </c>
       <c r="J8">
-        <v>4.3375000000000004</v>
+        <v>0.75</v>
       </c>
       <c r="K8">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L8">
-        <v>0.1</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0.15993870232100499</v>
-      </c>
-      <c r="N8" s="9">
-        <v>3.6092265943012181E-2</v>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="M8">
+        <v>0.54270516725411133</v>
+      </c>
+      <c r="N8">
+        <v>0.53532182103610682</v>
       </c>
       <c r="O8">
         <v>7.3624999999999998</v>
       </c>
       <c r="P8">
-        <v>3.0249999999999999</v>
+        <v>6.6124999999999998</v>
       </c>
       <c r="Q8">
-        <v>10.103799366691961</v>
+        <v>8.1885389499890149</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>31.789109429619018</v>
+        <v>76.787469661793068</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1036,53 +1045,53 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
-      <c r="E9" s="5">
-        <v>0.78749999999999998</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1.180571895311759</v>
-      </c>
-      <c r="G9" s="5">
-        <v>10.60467065614124</v>
-      </c>
-      <c r="H9" s="5">
-        <v>11.66070865838668</v>
-      </c>
-      <c r="I9" s="2">
-        <v>-0.51249999999999996</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0.6018960291348372</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0.57303370786516861</v>
+      <c r="E9">
+        <v>4.4375</v>
+      </c>
+      <c r="F9">
+        <v>4.7110243047558136</v>
+      </c>
+      <c r="G9">
+        <v>59.162109540785998</v>
+      </c>
+      <c r="H9">
+        <v>87.474442915484801</v>
+      </c>
+      <c r="I9">
+        <v>-4.3375000000000004</v>
+      </c>
+      <c r="J9">
+        <v>4.3375000000000004</v>
+      </c>
+      <c r="K9">
+        <v>0.1</v>
+      </c>
+      <c r="L9">
+        <v>0.1</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0.15993870232100499</v>
+      </c>
+      <c r="N9" s="9">
+        <v>3.6092265943012181E-2</v>
       </c>
       <c r="O9">
         <v>7.3624999999999998</v>
       </c>
       <c r="P9">
-        <v>6.85</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>6.36874541467696</v>
-      </c>
-      <c r="R9" s="7">
-        <f t="shared" si="0"/>
-        <v>80.068852872809089</v>
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="Q9">
+        <v>10.103799366691961</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>31.789109429619018</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -1093,53 +1102,53 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>40</v>
       </c>
-      <c r="E10" s="9">
-        <v>4.7374999999999998</v>
-      </c>
-      <c r="F10" s="8">
-        <v>4.9034426681669281</v>
-      </c>
-      <c r="G10" s="9">
-        <v>63.383339699516164</v>
-      </c>
-      <c r="H10" s="9">
-        <v>94.581669538191278</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-4.7374999999999998</v>
-      </c>
-      <c r="J10" s="8">
-        <v>4.7374999999999998</v>
-      </c>
-      <c r="K10" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L10" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M10">
-        <v>0.20229316971274439</v>
-      </c>
-      <c r="N10">
-        <v>1.7615522083227031E-2</v>
+      <c r="E10" s="5">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.180571895311759</v>
+      </c>
+      <c r="G10" s="5">
+        <v>10.60467065614124</v>
+      </c>
+      <c r="H10" s="5">
+        <v>11.66070865838668</v>
+      </c>
+      <c r="I10" s="2">
+        <v>-0.51249999999999996</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.6018960291348372</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.57303370786516861</v>
       </c>
       <c r="O10">
         <v>7.3624999999999998</v>
       </c>
-      <c r="P10" s="9">
-        <v>2.625</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>11.88738128434634</v>
-      </c>
-      <c r="R10" s="9">
-        <f t="shared" si="0"/>
-        <v>28.226659263914165</v>
+      <c r="P10">
+        <v>6.85</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>6.36874541467696</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" si="0"/>
+        <v>80.068852872809089</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -1150,167 +1159,167 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>40</v>
       </c>
-      <c r="E11" s="3">
-        <v>1.125</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1.874166481399131</v>
-      </c>
-      <c r="G11" s="3">
-        <v>16.069423223834988</v>
-      </c>
-      <c r="H11" s="3">
-        <v>19.35484515179661</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-0.625</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0.39458982945514431</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.30370370370370381</v>
-      </c>
-      <c r="O11" s="3">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P11" s="4">
-        <v>6.7374999999999998</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>8.6888006353721714</v>
-      </c>
-      <c r="R11" s="3">
-        <f t="shared" si="0"/>
-        <v>68.900347582723157</v>
+      <c r="E11" s="9">
+        <v>4.7374999999999998</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4.9034426681669281</v>
+      </c>
+      <c r="G11">
+        <v>63.383339699516164</v>
+      </c>
+      <c r="H11" s="9">
+        <v>94.581669538191278</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-4.7374999999999998</v>
+      </c>
+      <c r="J11" s="8">
+        <v>4.7374999999999998</v>
+      </c>
+      <c r="K11" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L11" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M11">
+        <v>0.20229316971274439</v>
+      </c>
+      <c r="N11">
+        <v>1.7615522083227031E-2</v>
+      </c>
+      <c r="O11">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P11" s="9">
+        <v>2.625</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>11.88738128434634</v>
+      </c>
+      <c r="R11" s="9">
+        <f t="shared" si="0"/>
+        <v>28.226659263914165</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
-      <c r="E12">
-        <v>1.6125</v>
-      </c>
-      <c r="F12">
-        <v>2.300815072968708</v>
-      </c>
-      <c r="G12">
-        <v>20.65077243018419</v>
-      </c>
-      <c r="H12">
-        <v>25.937014315622129</v>
-      </c>
-      <c r="I12">
-        <v>-1.4875</v>
-      </c>
-      <c r="J12">
-        <v>1.4875</v>
-      </c>
-      <c r="K12">
+      <c r="E12" s="13">
+        <v>1.125</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1.874166481399131</v>
+      </c>
+      <c r="G12" s="13">
+        <v>16.069423223834988</v>
+      </c>
+      <c r="H12" s="13">
+        <v>19.35484515179661</v>
+      </c>
+      <c r="I12" s="13">
+        <v>-0.625</v>
+      </c>
+      <c r="J12" s="13">
         <v>0.625</v>
       </c>
-      <c r="L12">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="M12" s="8">
-        <v>0.2084118813977244</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0.1083070452155627</v>
-      </c>
-      <c r="O12">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P12">
-        <v>5.875</v>
-      </c>
-      <c r="Q12">
-        <v>8.9753361010574739</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="0"/>
-        <v>59.908518436235028</v>
+      <c r="K12" s="13">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0.39458982945514431</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0.30370370370370381</v>
+      </c>
+      <c r="O12" s="13">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P12" s="14">
+        <v>6.7374999999999998</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>8.6888006353721714</v>
+      </c>
+      <c r="R12" s="13">
+        <f t="shared" si="0"/>
+        <v>68.900347582723157</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D13">
         <v>40</v>
       </c>
-      <c r="E13">
-        <v>1.95</v>
-      </c>
-      <c r="F13">
-        <v>2.962262648719725</v>
-      </c>
-      <c r="G13">
-        <v>27.571752185722779</v>
-      </c>
-      <c r="H13">
-        <v>39.643006676248042</v>
-      </c>
-      <c r="I13">
-        <v>-1.0249999999999999</v>
-      </c>
-      <c r="J13">
-        <v>1.0249999999999999</v>
-      </c>
-      <c r="K13">
-        <v>0.625</v>
-      </c>
-      <c r="L13">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="M13">
-        <v>0.4414534551168508</v>
-      </c>
-      <c r="N13">
-        <v>0.24283396430502971</v>
-      </c>
-      <c r="O13">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P13">
-        <v>6.3375000000000004</v>
-      </c>
-      <c r="Q13">
-        <v>8.0984407906973495</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="0"/>
-        <v>62.854686298651067</v>
+      <c r="E13" s="3">
+        <v>2.3374999999999999</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.0321199999999999</v>
+      </c>
+      <c r="G13" s="10">
+        <v>86.059039999999996</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46.409610000000001</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1.3374999999999999</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1.3374999999999999</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.480632</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.14780599999999999</v>
+      </c>
+      <c r="O13" s="3">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P13" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>6.0450059999999999</v>
+      </c>
+      <c r="R13" s="3">
+        <f t="shared" si="0"/>
+        <v>58.196024800000004</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -1321,53 +1330,53 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>40</v>
       </c>
       <c r="E14">
-        <v>0.92500000000000004</v>
+        <v>1.6125</v>
       </c>
       <c r="F14">
-        <v>1.2041594578792301</v>
+        <v>2.300815072968708</v>
       </c>
       <c r="G14">
-        <v>12.25000795772854</v>
+        <v>20.65077243018419</v>
       </c>
       <c r="H14">
-        <v>13.449333573631041</v>
+        <v>25.937014315622129</v>
       </c>
       <c r="I14">
-        <v>-0.75</v>
+        <v>-1.4875</v>
       </c>
       <c r="J14">
-        <v>0.75</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0.75</v>
+        <v>1.4875</v>
+      </c>
+      <c r="K14">
+        <v>0.625</v>
       </c>
       <c r="L14">
-        <v>0.95</v>
-      </c>
-      <c r="M14">
-        <v>0.56809595070697505</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0.64285714285714279</v>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0.2084118813977244</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0.1083070452155627</v>
       </c>
       <c r="O14">
         <v>7.3624999999999998</v>
       </c>
       <c r="P14">
-        <v>6.6124999999999998</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>3.0438303573580918</v>
-      </c>
-      <c r="R14" s="2">
-        <f t="shared" si="0"/>
-        <v>78.78719921916209</v>
+        <v>5.875</v>
+      </c>
+      <c r="Q14">
+        <v>8.9753361010574739</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="0"/>
+        <v>59.908518436235028</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -1378,53 +1387,53 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15">
         <v>40</v>
       </c>
-      <c r="E15" s="8">
-        <v>2.6475</v>
-      </c>
-      <c r="F15" s="8">
-        <v>3.3900958688509091</v>
-      </c>
-      <c r="G15" s="8">
-        <v>38.006997495968093</v>
-      </c>
-      <c r="H15" s="8">
-        <v>54.980546414369933</v>
-      </c>
-      <c r="I15" s="8">
-        <v>-2.1475</v>
-      </c>
-      <c r="J15" s="8">
-        <v>2.1475</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0.59096972449080432</v>
+      <c r="E15">
+        <v>1.95</v>
+      </c>
+      <c r="F15">
+        <v>2.962262648719725</v>
+      </c>
+      <c r="G15">
+        <v>27.571752185722779</v>
+      </c>
+      <c r="H15">
+        <v>39.643006676248042</v>
+      </c>
+      <c r="I15">
+        <v>-1.0249999999999999</v>
+      </c>
+      <c r="J15">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="K15">
+        <v>0.625</v>
+      </c>
+      <c r="L15">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M15">
+        <v>0.4414534551168508</v>
       </c>
       <c r="N15">
-        <v>0.26345157433240329</v>
+        <v>0.24283396430502971</v>
       </c>
       <c r="O15">
         <v>7.3624999999999998</v>
       </c>
-      <c r="P15" s="8">
-        <v>5.2149999999999999</v>
+      <c r="P15">
+        <v>6.3375000000000004</v>
       </c>
       <c r="Q15">
-        <v>6.7250011260039173</v>
+        <v>8.0984407906973495</v>
       </c>
       <c r="R15">
         <f t="shared" si="0"/>
-        <v>56.17943531686079</v>
+        <v>62.854686298651067</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1435,167 +1444,167 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>40</v>
       </c>
-      <c r="E16" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1.1011357772772621</v>
-      </c>
-      <c r="G16" s="4">
-        <v>11.5770652958153</v>
-      </c>
-      <c r="H16" s="4">
-        <v>12.28939207270566</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-0.47499999999999998</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="E16">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="F16">
+        <v>1.2041594578792301</v>
+      </c>
+      <c r="G16">
+        <v>12.25000795772854</v>
+      </c>
+      <c r="H16">
+        <v>13.449333573631041</v>
+      </c>
+      <c r="I16">
+        <v>-0.75</v>
+      </c>
+      <c r="J16">
+        <v>0.75</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="L16">
         <v>0.95</v>
       </c>
-      <c r="M16" s="3">
-        <v>0.58372431626369259</v>
-      </c>
-      <c r="N16" s="3">
-        <v>0.61043478260869555</v>
-      </c>
-      <c r="O16" s="3">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P16" s="4">
-        <v>6.8875000000000002</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>10.63603125622612</v>
-      </c>
-      <c r="R16" s="3">
-        <f t="shared" si="0"/>
-        <v>77.110474240717494</v>
+      <c r="M16">
+        <v>0.56809595070697505</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.64285714285714279</v>
+      </c>
+      <c r="O16">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P16">
+        <v>6.6124999999999998</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>3.0438303573580918</v>
+      </c>
+      <c r="R16" s="2">
+        <f t="shared" si="0"/>
+        <v>78.78719921916209</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>40</v>
       </c>
       <c r="E17" s="8">
-        <v>1.7875000000000001</v>
+        <v>2.6475</v>
       </c>
       <c r="F17" s="8">
-        <v>2.2290693125158758</v>
+        <v>3.3900958688509091</v>
       </c>
       <c r="G17" s="8">
-        <v>25.27360792801969</v>
+        <v>38.006997495968093</v>
       </c>
       <c r="H17" s="8">
-        <v>28.433024114525661</v>
-      </c>
-      <c r="I17">
-        <v>-0.53749999999999998</v>
-      </c>
-      <c r="J17">
-        <v>0.53749999999999998</v>
+        <v>54.980546414369933</v>
+      </c>
+      <c r="I17" s="8">
+        <v>-2.1475</v>
+      </c>
+      <c r="J17" s="8">
+        <v>2.1475</v>
       </c>
       <c r="K17" s="8">
-        <v>0.45</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="L17" s="8">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="M17">
-        <v>0.30622496369744567</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0.2516370439663238</v>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.59096972449080432</v>
+      </c>
+      <c r="N17">
+        <v>0.26345157433240329</v>
       </c>
       <c r="O17">
         <v>7.3624999999999998</v>
       </c>
-      <c r="P17">
-        <v>6.8250000000000002</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>28.857180417675409</v>
-      </c>
-      <c r="R17" s="8">
-        <f t="shared" si="0"/>
-        <v>56.273849973023466</v>
+      <c r="P17" s="8">
+        <v>5.2149999999999999</v>
+      </c>
+      <c r="Q17">
+        <v>6.7250011260039173</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="0"/>
+        <v>56.17943531686079</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>40</v>
       </c>
-      <c r="E18">
-        <v>1.54575</v>
-      </c>
-      <c r="F18">
-        <v>1.9138893646185511</v>
-      </c>
-      <c r="G18">
-        <v>20.83477978312537</v>
-      </c>
-      <c r="H18">
-        <v>22.262627850969981</v>
-      </c>
-      <c r="I18">
-        <v>-0.29575000000000001</v>
-      </c>
-      <c r="J18">
-        <v>0.29575000000000001</v>
-      </c>
-      <c r="K18">
+      <c r="E18" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1.1011357772772621</v>
+      </c>
+      <c r="G18" s="4">
+        <v>11.5770652958153</v>
+      </c>
+      <c r="H18" s="4">
+        <v>12.28939207270566</v>
+      </c>
+      <c r="I18" s="4">
+        <v>-0.47499999999999998</v>
+      </c>
+      <c r="J18" s="4">
         <v>0.47499999999999998</v>
       </c>
-      <c r="L18">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="M18" s="8">
-        <v>0.30258790204508151</v>
-      </c>
-      <c r="N18">
-        <v>0.34440753045404221</v>
-      </c>
-      <c r="O18">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P18">
-        <v>7.0667500000000008</v>
-      </c>
-      <c r="Q18">
-        <v>13.249658892708251</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="0"/>
-        <v>62.689995030011083</v>
+      <c r="K18" s="3">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.58372431626369259</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.61043478260869555</v>
+      </c>
+      <c r="O18" s="3">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P18" s="4">
+        <v>6.8875000000000002</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>10.63603125622612</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="0"/>
+        <v>77.110474240717494</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -1606,53 +1615,53 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>40</v>
       </c>
-      <c r="E19" s="2">
-        <v>1.175</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1.553222456700907</v>
-      </c>
-      <c r="G19" s="2">
-        <v>17.503631376793141</v>
-      </c>
-      <c r="H19" s="2">
-        <v>17.51763497287153</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0.56332432118004616</v>
-      </c>
-      <c r="N19" s="2">
-        <v>0.5006501950585176</v>
+      <c r="E19">
+        <v>1.7875000000000001</v>
+      </c>
+      <c r="F19">
+        <v>2.2290693125158758</v>
+      </c>
+      <c r="G19">
+        <v>25.27360792801969</v>
+      </c>
+      <c r="H19">
+        <v>28.433024114525661</v>
+      </c>
+      <c r="I19">
+        <v>-0.53749999999999998</v>
+      </c>
+      <c r="J19">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="K19" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="L19" s="16">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="M19">
+        <v>0.30622496369744567</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0.2516370439663238</v>
       </c>
       <c r="O19">
         <v>7.3624999999999998</v>
       </c>
-      <c r="P19" s="5">
-        <v>7.5125000000000002</v>
-      </c>
-      <c r="Q19">
-        <v>19.864633801116721</v>
-      </c>
-      <c r="R19" s="2">
-        <f t="shared" si="0"/>
-        <v>70.377698278393893</v>
+      <c r="P19">
+        <v>6.8250000000000002</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>28.857180417675409</v>
+      </c>
+      <c r="R19" s="16">
+        <f t="shared" si="0"/>
+        <v>56.273849973023466</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
@@ -1663,53 +1672,53 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>1.3875</v>
+        <v>1.54575</v>
       </c>
       <c r="F20">
-        <v>1.758905909933786</v>
+        <v>1.9138893646185511</v>
       </c>
       <c r="G20">
-        <v>19.23130994822171</v>
+        <v>20.83477978312537</v>
       </c>
       <c r="H20">
-        <v>21.09914905425741</v>
+        <v>22.262627850969981</v>
       </c>
       <c r="I20">
-        <v>-0.58750000000000002</v>
+        <v>-0.29575000000000001</v>
       </c>
       <c r="J20">
-        <v>0.58750000000000002</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="L20" s="8">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="M20">
-        <v>0.42118174863064461</v>
+        <v>0.29575000000000001</v>
+      </c>
+      <c r="K20">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="L20">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0.30258790204508151</v>
       </c>
       <c r="N20">
-        <v>0.42015855039637579</v>
+        <v>0.34440753045404221</v>
       </c>
       <c r="O20">
         <v>7.3624999999999998</v>
       </c>
       <c r="P20">
-        <v>6.7750000000000004</v>
+        <v>7.0667500000000008</v>
       </c>
       <c r="Q20">
-        <v>11.99440628229058</v>
+        <v>13.249658892708251</v>
       </c>
       <c r="R20">
         <f t="shared" si="0"/>
-        <v>67.989045078598892</v>
+        <v>62.689995030011083</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -1720,224 +1729,224 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <v>40</v>
       </c>
-      <c r="E21" s="3">
-        <v>1.3374999999999999</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1.64506838763621</v>
-      </c>
-      <c r="G21" s="3">
-        <v>17.943460338680929</v>
-      </c>
-      <c r="H21" s="3">
-        <v>20.314927772364221</v>
-      </c>
-      <c r="I21" s="10">
-        <v>-1.2124999999999999</v>
-      </c>
-      <c r="J21" s="10">
-        <v>1.2124999999999999</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0.48635281886927229</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0.40957446808510639</v>
-      </c>
-      <c r="O21" s="3">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P21" s="10">
-        <v>6.15</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>8.6568410104693605</v>
-      </c>
-      <c r="R21" s="3">
-        <f t="shared" si="0"/>
-        <v>65.895502982500702</v>
+      <c r="E21" s="2">
+        <v>1.175</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1.553222456700907</v>
+      </c>
+      <c r="G21" s="2">
+        <v>17.503631376793141</v>
+      </c>
+      <c r="H21" s="2">
+        <v>17.51763497287153</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.56332432118004616</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0.5006501950585176</v>
+      </c>
+      <c r="O21">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P21" s="5">
+        <v>7.5125000000000002</v>
+      </c>
+      <c r="Q21">
+        <v>19.864633801116721</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" si="0"/>
+        <v>70.377698278393893</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D22">
         <v>40</v>
       </c>
       <c r="E22">
-        <v>1.6125</v>
+        <v>1.3875</v>
       </c>
       <c r="F22">
-        <v>2.108020398383279</v>
-      </c>
-      <c r="G22" s="8">
-        <v>21.91852346999406</v>
-      </c>
-      <c r="H22" s="8">
-        <v>27.060605545125672</v>
+        <v>1.758905909933786</v>
+      </c>
+      <c r="G22">
+        <v>19.23130994822171</v>
+      </c>
+      <c r="H22">
+        <v>21.09914905425741</v>
       </c>
       <c r="I22">
-        <v>-1.4875</v>
+        <v>-0.58750000000000002</v>
       </c>
       <c r="J22">
-        <v>1.4875</v>
-      </c>
-      <c r="K22">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="L22">
-        <v>0.75</v>
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="L22" s="16">
+        <v>0.77500000000000002</v>
       </c>
       <c r="M22">
-        <v>0.40986085901277652</v>
-      </c>
-      <c r="N22" s="8">
-        <v>0.35608048993875763</v>
+        <v>0.42118174863064461</v>
+      </c>
+      <c r="N22">
+        <v>0.42015855039637579</v>
       </c>
       <c r="O22">
         <v>7.3624999999999998</v>
       </c>
       <c r="P22">
-        <v>5.875</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>28.298557734396312</v>
+        <v>6.7750000000000004</v>
+      </c>
+      <c r="Q22">
+        <v>11.99440628229058</v>
       </c>
       <c r="R22">
         <f t="shared" si="0"/>
-        <v>59.339862275921021</v>
+        <v>67.989045078598892</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23">
         <v>40</v>
       </c>
-      <c r="E23">
-        <v>1.575</v>
-      </c>
-      <c r="F23" s="8">
-        <v>1.9811612756158949</v>
-      </c>
-      <c r="G23">
-        <v>21.53143833290892</v>
-      </c>
-      <c r="H23">
-        <v>25.629764653990659</v>
-      </c>
-      <c r="I23">
-        <v>-1.375</v>
-      </c>
-      <c r="J23">
-        <v>1.375</v>
-      </c>
-      <c r="K23">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L23">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="M23">
-        <v>0.51651925791836673</v>
-      </c>
-      <c r="N23">
-        <v>0.3908045977011495</v>
-      </c>
-      <c r="O23">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P23">
-        <v>5.9874999999999998</v>
-      </c>
-      <c r="Q23">
-        <v>25.068140193665752</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="0"/>
-        <v>62.324433714515138</v>
+      <c r="E23" s="13">
+        <v>1.3374999999999999</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1.64506838763621</v>
+      </c>
+      <c r="G23" s="13">
+        <v>17.943460338680929</v>
+      </c>
+      <c r="H23" s="13">
+        <v>20.314927772364221</v>
+      </c>
+      <c r="I23" s="18">
+        <v>-1.2124999999999999</v>
+      </c>
+      <c r="J23" s="18">
+        <v>1.2124999999999999</v>
+      </c>
+      <c r="K23" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="M23" s="13">
+        <v>0.48635281886927229</v>
+      </c>
+      <c r="N23" s="13">
+        <v>0.40957446808510639</v>
+      </c>
+      <c r="O23" s="13">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P23" s="15">
+        <v>6.15</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>8.6568410104693605</v>
+      </c>
+      <c r="R23" s="13">
+        <f t="shared" si="0"/>
+        <v>65.895502982500702</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>40</v>
       </c>
-      <c r="E24" s="2">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1.6163229875244609</v>
-      </c>
-      <c r="G24" s="2">
-        <v>16.959333354553941</v>
-      </c>
-      <c r="H24" s="2">
-        <v>19.31765935199876</v>
-      </c>
-      <c r="I24">
-        <v>-1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="M24">
-        <v>0.60524066593152814</v>
-      </c>
-      <c r="N24">
-        <v>0.47764705882352942</v>
-      </c>
-      <c r="O24">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P24" s="2">
-        <v>6.3624999999999998</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>15.42797080937598</v>
-      </c>
-      <c r="R24" s="2">
-        <f t="shared" si="0"/>
-        <v>70.317214060405519</v>
+      <c r="E24" s="10">
+        <v>2.35</v>
+      </c>
+      <c r="F24" s="10">
+        <v>3.1224989999999999</v>
+      </c>
+      <c r="G24" s="10">
+        <v>83.175340000000006</v>
+      </c>
+      <c r="H24" s="10">
+        <v>45.630139999999997</v>
+      </c>
+      <c r="I24" s="10">
+        <v>1.45</v>
+      </c>
+      <c r="J24" s="10">
+        <v>1.45</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0.397339</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0.27276099999999998</v>
+      </c>
+      <c r="O24" s="3">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P24" s="3">
+        <v>7.1124999999999998</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>16.09769</v>
+      </c>
+      <c r="R24" s="10">
+        <f t="shared" si="0"/>
+        <v>55.178089999999997</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
@@ -1948,53 +1957,53 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>40</v>
       </c>
       <c r="E25">
-        <v>1.3374999999999999</v>
+        <v>1.6125</v>
       </c>
       <c r="F25">
-        <v>1.6639561292293741</v>
-      </c>
-      <c r="G25">
-        <v>18.34025655716832</v>
-      </c>
-      <c r="H25">
-        <v>20.450053138133629</v>
-      </c>
-      <c r="I25" s="2">
-        <v>-0.66249999999999998</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0.66249999999999998</v>
+        <v>2.108020398383279</v>
+      </c>
+      <c r="G25" s="16">
+        <v>21.91852346999406</v>
+      </c>
+      <c r="H25" s="16">
+        <v>27.060605545125672</v>
+      </c>
+      <c r="I25">
+        <v>-1.4875</v>
+      </c>
+      <c r="J25">
+        <v>1.4875</v>
       </c>
       <c r="K25">
-        <v>0.625</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="L25">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="M25">
-        <v>0.53171655650664218</v>
-      </c>
-      <c r="N25" s="2">
-        <v>0.4866071428571429</v>
+        <v>0.40986085901277652</v>
+      </c>
+      <c r="N25" s="16">
+        <v>0.35608048993875763</v>
       </c>
       <c r="O25">
         <v>7.3624999999999998</v>
       </c>
       <c r="P25">
-        <v>6.7</v>
-      </c>
-      <c r="Q25">
-        <v>19.38518868534884</v>
+        <v>5.875</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>28.298557734396312</v>
       </c>
       <c r="R25">
         <f t="shared" si="0"/>
-        <v>68.724345728611127</v>
+        <v>59.339862275921021</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
@@ -2005,148 +2014,379 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>40</v>
+      </c>
+      <c r="E26">
+        <v>1.575</v>
+      </c>
+      <c r="F26" s="16">
+        <v>1.9811612756158949</v>
+      </c>
+      <c r="G26">
+        <v>21.53143833290892</v>
+      </c>
+      <c r="H26">
+        <v>25.629764653990659</v>
+      </c>
+      <c r="I26">
+        <v>-1.375</v>
+      </c>
+      <c r="J26">
+        <v>1.375</v>
+      </c>
+      <c r="K26">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L26">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="M26">
+        <v>0.51651925791836673</v>
+      </c>
+      <c r="N26">
+        <v>0.3908045977011495</v>
+      </c>
+      <c r="O26">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P26">
+        <v>5.9874999999999998</v>
+      </c>
+      <c r="Q26">
+        <v>25.068140193665752</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="0"/>
+        <v>62.324433714515138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1.6163229875244609</v>
+      </c>
+      <c r="G27" s="2">
+        <v>16.959333354553941</v>
+      </c>
+      <c r="H27" s="2">
+        <v>19.31765935199876</v>
+      </c>
+      <c r="I27">
+        <v>-1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M27">
+        <v>0.60524066593152814</v>
+      </c>
+      <c r="N27">
+        <v>0.47764705882352942</v>
+      </c>
+      <c r="O27">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P27" s="2">
+        <v>6.3624999999999998</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>15.42797080937598</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="0"/>
+        <v>70.317214060405519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>40</v>
+      </c>
+      <c r="E28">
+        <v>1.3374999999999999</v>
+      </c>
+      <c r="F28">
+        <v>1.6639561292293741</v>
+      </c>
+      <c r="G28">
+        <v>18.34025655716832</v>
+      </c>
+      <c r="H28">
+        <v>20.450053138133629</v>
+      </c>
+      <c r="I28" s="2">
+        <v>-0.66249999999999998</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="K28">
+        <v>0.625</v>
+      </c>
+      <c r="L28">
+        <v>0.85</v>
+      </c>
+      <c r="M28">
+        <v>0.53171655650664218</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0.4866071428571429</v>
+      </c>
+      <c r="O28">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P28">
+        <v>6.7</v>
+      </c>
+      <c r="Q28">
+        <v>19.38518868534884</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="0"/>
+        <v>68.724345728611127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
         <v>21</v>
       </c>
-      <c r="D26">
-        <v>40</v>
-      </c>
-      <c r="E26" s="8">
+      <c r="D29">
+        <v>40</v>
+      </c>
+      <c r="E29">
         <v>1.625</v>
       </c>
-      <c r="F26">
+      <c r="F29">
         <v>1.8641351882307251</v>
       </c>
-      <c r="G26">
+      <c r="G29">
         <v>21.530934343434339</v>
       </c>
-      <c r="H26">
+      <c r="H29">
         <v>24.82799855351675</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I29" s="8">
         <v>-1.6</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J29" s="8">
         <v>1.6</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K29" s="8">
         <v>0.3</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L29" s="16">
         <v>0.7</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M29" s="5">
         <v>0.63374952476318069</v>
       </c>
-      <c r="N26">
+      <c r="N29">
         <v>0.39878787878787869</v>
       </c>
-      <c r="O26">
-        <v>7.3624999999999998</v>
-      </c>
-      <c r="P26" s="8">
+      <c r="O29">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P29" s="8">
         <v>5.7625000000000002</v>
       </c>
-      <c r="Q26">
+      <c r="Q29">
         <v>19.63242700413684</v>
       </c>
-      <c r="R26" s="8">
+      <c r="R29" s="16">
         <f t="shared" si="0"/>
         <v>58.898693790865536</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.2374999999999998</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2.9485169999999998</v>
+      </c>
+      <c r="G30" s="8">
+        <v>77.599369999999993</v>
+      </c>
+      <c r="H30" s="8">
+        <v>45.988520000000001</v>
+      </c>
+      <c r="I30">
+        <v>0.8125</v>
+      </c>
+      <c r="J30">
+        <v>0.8125</v>
+      </c>
+      <c r="K30">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0.29924200000000001</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0.23202800000000001</v>
+      </c>
+      <c r="O30" s="13">
+        <v>7.3624999999999998</v>
+      </c>
+      <c r="P30">
+        <v>6.4749999999999996</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>14.04659</v>
+      </c>
+      <c r="R30" s="8">
+        <f t="shared" si="0"/>
+        <v>55.454021000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E31" s="8"/>
+    </row>
+    <row r="33" spans="1:14" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="A37:N37"/>
+    <mergeCell ref="A35:N35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
